--- a/Object-Models-Updated.xlsx
+++ b/Object-Models-Updated.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O248"/>
+  <dimension ref="A1:P248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,10 +488,15 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>模型发布时间</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>是否新增</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>核实情况</t>
         </is>
@@ -553,6 +558,7 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,6 +616,7 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,6 +666,7 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -712,6 +720,7 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -761,6 +770,7 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -818,6 +828,7 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -875,6 +886,7 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -920,6 +932,7 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -969,6 +982,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1014,6 +1028,7 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1063,6 +1078,7 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1112,6 +1128,7 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1161,6 +1178,7 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1206,6 +1224,7 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1251,6 +1270,7 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1296,6 +1316,7 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1341,6 +1362,7 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1394,6 +1416,7 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1447,6 +1470,7 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1492,6 +1516,7 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1549,6 +1574,7 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1594,6 +1620,7 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1639,6 +1666,7 @@
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1684,6 +1712,7 @@
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1729,6 +1758,7 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1778,6 +1808,7 @@
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1823,6 +1854,7 @@
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1876,6 +1908,7 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1921,6 +1954,7 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1966,6 +2000,7 @@
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2015,6 +2050,7 @@
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2064,6 +2100,7 @@
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2117,6 +2154,7 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2166,6 +2204,7 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2211,6 +2250,7 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2260,6 +2300,7 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2309,6 +2350,7 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2366,6 +2408,7 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2415,6 +2458,7 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2468,6 +2512,7 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2521,6 +2566,7 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2566,6 +2612,7 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2615,6 +2662,7 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2664,6 +2712,7 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2713,6 +2762,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2762,6 +2812,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2815,6 +2866,7 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2856,6 +2908,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2897,6 +2950,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2942,6 +2996,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2991,6 +3046,7 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3040,6 +3096,7 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3085,6 +3142,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3134,6 +3192,7 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3187,6 +3246,7 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3236,6 +3296,7 @@
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3281,6 +3342,7 @@
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3330,6 +3392,7 @@
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3379,6 +3442,7 @@
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3424,6 +3488,7 @@
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3469,6 +3534,7 @@
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3522,6 +3588,7 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3567,6 +3634,7 @@
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3620,6 +3688,7 @@
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3669,6 +3738,7 @@
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3718,6 +3788,7 @@
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3767,6 +3838,7 @@
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3816,6 +3888,7 @@
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3861,6 +3934,7 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3910,6 +3984,7 @@
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3967,6 +4042,7 @@
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4012,6 +4088,7 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4061,6 +4138,7 @@
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4110,6 +4188,7 @@
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4159,6 +4238,7 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4208,6 +4288,7 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4257,6 +4338,7 @@
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4318,6 +4400,7 @@
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4375,6 +4458,7 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4424,6 +4508,7 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4465,6 +4550,7 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4522,6 +4608,7 @@
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4563,6 +4650,7 @@
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4608,6 +4696,7 @@
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4653,6 +4742,7 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4702,6 +4792,7 @@
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4747,6 +4838,7 @@
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4796,6 +4888,7 @@
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4845,6 +4938,7 @@
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4894,6 +4988,7 @@
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4943,6 +5038,7 @@
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4992,6 +5088,7 @@
       </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5041,6 +5138,7 @@
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5094,6 +5192,7 @@
       </c>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5143,6 +5242,7 @@
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5192,6 +5292,7 @@
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5241,6 +5342,7 @@
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5290,6 +5392,7 @@
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5339,6 +5442,7 @@
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5388,6 +5492,7 @@
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5437,6 +5542,7 @@
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5486,6 +5592,7 @@
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5535,6 +5642,7 @@
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5584,6 +5692,7 @@
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5633,6 +5742,7 @@
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5682,6 +5792,7 @@
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5731,6 +5842,7 @@
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5780,6 +5892,7 @@
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5829,6 +5942,7 @@
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5878,6 +5992,7 @@
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5927,6 +6042,7 @@
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5976,6 +6092,7 @@
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6025,6 +6142,7 @@
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6074,6 +6192,7 @@
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6123,6 +6242,7 @@
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6172,6 +6292,7 @@
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6221,6 +6342,7 @@
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6270,6 +6392,7 @@
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6319,6 +6442,7 @@
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6368,6 +6492,7 @@
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6417,6 +6542,7 @@
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6466,6 +6592,7 @@
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6515,6 +6642,7 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6564,6 +6692,7 @@
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6613,6 +6742,7 @@
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6662,6 +6792,7 @@
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6711,6 +6842,7 @@
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6760,6 +6892,7 @@
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6809,6 +6942,7 @@
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6858,6 +6992,7 @@
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6907,6 +7042,7 @@
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6956,6 +7092,7 @@
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7009,6 +7146,7 @@
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7058,6 +7196,7 @@
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7107,6 +7246,7 @@
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7156,6 +7296,7 @@
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7205,6 +7346,7 @@
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7254,6 +7396,7 @@
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7303,6 +7446,7 @@
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7352,6 +7496,7 @@
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7401,6 +7546,7 @@
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7450,6 +7596,7 @@
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7499,6 +7646,7 @@
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7548,6 +7696,7 @@
       </c>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7597,6 +7746,7 @@
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7654,6 +7804,7 @@
       </c>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7695,6 +7846,7 @@
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7744,6 +7896,7 @@
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7797,6 +7950,7 @@
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7842,6 +7996,7 @@
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7903,6 +8058,7 @@
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7944,6 +8100,7 @@
       </c>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7993,6 +8150,7 @@
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8050,6 +8208,7 @@
       </c>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8095,6 +8254,7 @@
       </c>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8140,6 +8300,7 @@
       </c>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8193,6 +8354,7 @@
       </c>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8246,6 +8408,7 @@
       </c>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8303,12 +8466,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr">
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr">
+      <c r="P160" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -8370,12 +8534,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr">
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr">
+      <c r="P161" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -8433,12 +8598,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr">
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr">
+      <c r="P162" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -8496,12 +8662,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr">
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
+      <c r="P163" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -8559,12 +8726,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr">
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
+      <c r="P164" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -8630,12 +8798,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O165" t="inlineStr">
+      <c r="P165" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:访问失败(401 Unauthorized(需同意License)) | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -8697,12 +8866,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr">
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O166" t="inlineStr">
+      <c r="P166" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -8756,12 +8926,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr">
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr">
+      <c r="P167" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -8823,12 +8994,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr">
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr">
+      <c r="P168" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -8890,12 +9062,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr">
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr">
+      <c r="P169" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -8953,12 +9126,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr">
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O170" t="inlineStr">
+      <c r="P170" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -9020,12 +9194,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr">
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr">
+      <c r="P171" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9087,12 +9262,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr">
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr">
+      <c r="P172" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9154,12 +9330,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr">
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
+      <c r="P173" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9221,12 +9398,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr">
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
+      <c r="P174" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9286,6 +9464,7 @@
       </c>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9343,12 +9522,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr">
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr">
+      <c r="P176" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9406,12 +9586,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr">
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr">
+      <c r="P177" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -9469,12 +9650,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr">
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr">
+      <c r="P178" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -9532,12 +9714,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr">
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr">
+      <c r="P179" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:未尝试</t>
         </is>
@@ -9591,12 +9774,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr">
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr">
+      <c r="P180" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:访问失败(401 Unauthorized(需同意License)) | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9658,12 +9842,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr">
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr">
+      <c r="P181" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9725,12 +9910,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr">
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr">
+      <c r="P182" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -9788,12 +9974,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr">
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr">
+      <c r="P183" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -9847,12 +10034,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr">
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr">
+      <c r="P184" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -9902,12 +10090,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr">
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr">
+      <c r="P185" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -9969,12 +10158,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr">
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr">
+      <c r="P186" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10036,12 +10226,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr">
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr">
+      <c r="P187" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10099,12 +10290,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr">
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr">
+      <c r="P188" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -10166,12 +10358,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr">
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr">
+      <c r="P189" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10229,12 +10422,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr">
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr">
+      <c r="P190" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -10300,12 +10494,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr">
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr">
+      <c r="P191" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:访问失败(401 Unauthorized(需同意License)) | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10367,12 +10562,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr">
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr">
+      <c r="P192" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10438,12 +10634,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr">
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr">
+      <c r="P193" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:未尝试 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10501,12 +10698,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr">
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr">
+      <c r="P194" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -10566,6 +10764,7 @@
       </c>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10619,12 +10818,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr">
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr">
+      <c r="P196" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -10678,12 +10878,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr">
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
+      <c r="P197" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:未尝试</t>
         </is>
@@ -10737,12 +10938,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr">
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O198" t="inlineStr">
+      <c r="P198" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -10808,12 +11010,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr">
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr">
+      <c r="P199" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:未尝试 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10879,12 +11082,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr">
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr">
+      <c r="P200" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -10942,12 +11146,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr">
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr">
+      <c r="P201" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11005,12 +11210,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr">
+      <c r="P202" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11076,12 +11282,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr">
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr">
+      <c r="P203" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -11143,12 +11350,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr">
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr">
+      <c r="P204" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -11210,12 +11418,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr">
+      <c r="P205" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -11277,12 +11486,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr">
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr">
+      <c r="P206" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -11344,12 +11554,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr">
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
+      <c r="P207" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -11411,12 +11622,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr">
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr">
+      <c r="P208" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -11474,12 +11686,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr">
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr">
+      <c r="P209" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11537,12 +11750,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr">
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr">
+      <c r="P210" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11600,12 +11814,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr">
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O211" t="inlineStr">
+      <c r="P211" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -11663,12 +11878,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr">
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O212" t="inlineStr">
+      <c r="P212" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11730,12 +11946,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr">
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="P213" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -11789,12 +12006,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr">
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
+      <c r="P214" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11852,12 +12070,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr">
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr">
+      <c r="P215" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -11911,12 +12130,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr">
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O216" t="inlineStr">
+      <c r="P216" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -11974,12 +12194,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr">
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr">
+      <c r="P217" t="inlineStr">
         <is>
           <t>web_search:未执行 | HuggingFace:未尝试</t>
         </is>
@@ -12037,12 +12258,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr">
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr">
+      <c r="P218" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12100,12 +12322,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr">
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr">
+      <c r="P219" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:未尝试</t>
         </is>
@@ -12163,12 +12386,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr">
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O220" t="inlineStr">
+      <c r="P220" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12226,12 +12450,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr">
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr">
+      <c r="P221" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12289,12 +12514,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr">
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr">
+      <c r="P222" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12352,12 +12578,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr">
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr">
+      <c r="P223" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12411,12 +12638,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr">
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr">
+      <c r="P224" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12470,12 +12698,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr">
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr">
+      <c r="P225" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12533,12 +12762,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="P226" t="inlineStr">
         <is>
           <t>web_search:未执行 | 官网链接:无</t>
         </is>
@@ -12600,12 +12830,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr">
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr">
+      <c r="P227" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -12667,12 +12898,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr">
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
+      <c r="P228" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -12734,12 +12966,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr">
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
+      <c r="P229" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -12801,12 +13034,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr">
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
+      <c r="P230" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -12868,12 +13102,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr">
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr">
+      <c r="P231" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -12935,12 +13170,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr">
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr">
+      <c r="P232" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -13002,12 +13238,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr">
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr">
+      <c r="P233" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -13071,6 +13308,7 @@
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13126,6 +13364,7 @@
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13183,12 +13422,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr">
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr">
+      <c r="P236" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -13246,12 +13486,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr">
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr">
+      <c r="P237" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -13317,12 +13558,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr">
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr">
+      <c r="P238" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:已成功(params=119.4B,license=Apache-2.0) | 官网链接:有(未逐个验证可用性)</t>
         </is>
@@ -13380,12 +13622,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr">
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
+      <c r="P239" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:已成功(params=未公开(MoE),license=Apache-2.0)</t>
         </is>
@@ -13443,12 +13686,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr">
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr">
+      <c r="P240" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:访问失败(401 Unauthorized(需同意License))</t>
         </is>
@@ -13506,12 +13750,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr">
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O241" t="inlineStr">
+      <c r="P241" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -13565,12 +13810,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr">
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
+      <c r="P242" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -13624,12 +13870,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr">
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
+      <c r="P243" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -13691,12 +13938,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr">
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr">
+      <c r="P244" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:已成功(params=809M,license=MIT)</t>
         </is>
@@ -13754,12 +14002,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr">
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr">
+      <c r="P245" t="inlineStr">
         <is>
           <t>web_search:已执行 | 官网链接:无</t>
         </is>
@@ -13821,12 +14070,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr">
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr">
+      <c r="P246" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:已成功(params=4.7B,license=Apache-2.0)</t>
         </is>
@@ -13884,12 +14134,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr">
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr">
+      <c r="P247" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:访问失败(401 Unauthorized(需同意License))</t>
         </is>
@@ -13947,12 +14198,13 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr">
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
+      <c r="P248" t="inlineStr">
         <is>
           <t>web_search:已执行 | HuggingFace:访问失败(401 Unauthorized(需同意License))</t>
         </is>

--- a/Object-Models-Updated.xlsx
+++ b/Object-Models-Updated.xlsx
@@ -8466,7 +8466,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
           <t>New</t>
@@ -8534,7 +8538,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>New</t>
@@ -8598,7 +8606,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O162" t="inlineStr">
         <is>
           <t>New</t>
@@ -8662,7 +8674,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O163" t="inlineStr">
         <is>
           <t>New</t>
@@ -8726,7 +8742,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr">
         <is>
           <t>New</t>
@@ -8798,7 +8818,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>New</t>
@@ -8866,7 +8890,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O166" t="inlineStr">
         <is>
           <t>New</t>
@@ -8926,7 +8954,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O167" t="inlineStr">
         <is>
           <t>New</t>
@@ -8994,7 +9026,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>New</t>
@@ -9062,7 +9098,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>New</t>
@@ -9126,7 +9166,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>New</t>
@@ -9194,7 +9238,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>New</t>
@@ -9262,7 +9310,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>New</t>
@@ -9330,7 +9382,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>New</t>
@@ -9398,7 +9454,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>New</t>
@@ -9462,7 +9522,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
     </row>
@@ -9522,7 +9586,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
       <c r="O176" t="inlineStr">
         <is>
           <t>New</t>
@@ -9586,7 +9654,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr">
         <is>
           <t>New</t>
@@ -9650,7 +9722,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr">
         <is>
           <t>New</t>
@@ -9714,7 +9790,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr">
         <is>
           <t>New</t>
@@ -9774,7 +9854,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr">
         <is>
           <t>New</t>
@@ -9842,7 +9926,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr">
         <is>
           <t>New</t>
@@ -9910,7 +9998,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr">
         <is>
           <t>New</t>
@@ -9974,7 +10066,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr">
         <is>
           <t>New</t>
@@ -10034,7 +10130,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
           <t>New</t>
@@ -10090,7 +10190,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr">
         <is>
           <t>New</t>
@@ -10158,7 +10262,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr">
         <is>
           <t>New</t>
@@ -10226,7 +10334,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr">
         <is>
           <t>New</t>
@@ -10290,7 +10402,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>New</t>
@@ -10358,7 +10474,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr">
         <is>
           <t>New</t>
@@ -10422,7 +10542,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="O190" t="inlineStr">
         <is>
           <t>New</t>
@@ -10494,7 +10618,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>New</t>
@@ -10562,7 +10690,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr">
         <is>
           <t>New</t>
@@ -10634,7 +10766,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="O193" t="inlineStr">
         <is>
           <t>New</t>
@@ -10698,7 +10834,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr">
         <is>
           <t>New</t>
@@ -10762,7 +10902,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
     </row>
@@ -10818,7 +10962,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O196" t="inlineStr">
         <is>
           <t>New</t>
@@ -10878,7 +11026,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O197" t="inlineStr">
         <is>
           <t>New</t>
@@ -10938,7 +11090,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr">
         <is>
           <t>New</t>
@@ -11010,7 +11166,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr">
         <is>
           <t>New</t>
@@ -11082,7 +11242,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr">
         <is>
           <t>New</t>
@@ -11146,7 +11310,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="O201" t="inlineStr">
         <is>
           <t>New</t>
@@ -11210,7 +11378,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr">
         <is>
           <t>New</t>
@@ -11282,7 +11454,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
       <c r="O203" t="inlineStr">
         <is>
           <t>New</t>
@@ -11350,7 +11526,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr">
         <is>
           <t>New</t>
@@ -11418,7 +11598,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
       <c r="O205" t="inlineStr">
         <is>
           <t>New</t>
@@ -11486,7 +11670,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>New</t>
@@ -11554,7 +11742,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
       <c r="O207" t="inlineStr">
         <is>
           <t>New</t>
@@ -11622,7 +11814,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
       <c r="O208" t="inlineStr">
         <is>
           <t>New</t>
@@ -11686,7 +11882,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
       <c r="O209" t="inlineStr">
         <is>
           <t>New</t>
@@ -11750,7 +11950,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr">
         <is>
           <t>New</t>
@@ -11814,7 +12018,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
       <c r="O211" t="inlineStr">
         <is>
           <t>New</t>
@@ -11878,7 +12086,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
       <c r="O212" t="inlineStr">
         <is>
           <t>New</t>
@@ -11946,7 +12158,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="O213" t="inlineStr">
         <is>
           <t>New</t>
@@ -12006,7 +12222,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="O214" t="inlineStr">
         <is>
           <t>New</t>
@@ -12070,7 +12290,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="O215" t="inlineStr">
         <is>
           <t>New</t>
@@ -12130,7 +12354,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
       <c r="O216" t="inlineStr">
         <is>
           <t>New</t>
@@ -12194,7 +12422,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
       <c r="O217" t="inlineStr">
         <is>
           <t>New</t>
@@ -12258,7 +12490,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
       <c r="O218" t="inlineStr">
         <is>
           <t>New</t>
@@ -12322,7 +12558,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
       <c r="O219" t="inlineStr">
         <is>
           <t>New</t>
@@ -12386,7 +12626,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>New</t>
@@ -12450,7 +12694,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
       <c r="O221" t="inlineStr">
         <is>
           <t>New</t>
@@ -12514,7 +12762,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="O222" t="inlineStr">
         <is>
           <t>New</t>
@@ -12578,7 +12830,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>New</t>
@@ -12638,7 +12894,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
       <c r="O224" t="inlineStr">
         <is>
           <t>New</t>
@@ -12698,7 +12958,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
       <c r="O225" t="inlineStr">
         <is>
           <t>New</t>
@@ -12762,7 +13026,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
       <c r="O226" t="inlineStr">
         <is>
           <t>New</t>
@@ -12830,7 +13098,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="O227" t="inlineStr">
         <is>
           <t>New</t>
@@ -12898,7 +13170,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
       <c r="O228" t="inlineStr">
         <is>
           <t>New</t>
@@ -12966,7 +13242,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
       <c r="O229" t="inlineStr">
         <is>
           <t>New</t>
@@ -13034,7 +13314,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
       <c r="O230" t="inlineStr">
         <is>
           <t>New</t>
@@ -13102,7 +13386,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
       <c r="O231" t="inlineStr">
         <is>
           <t>New</t>
@@ -13170,7 +13458,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="O232" t="inlineStr">
         <is>
           <t>New</t>
@@ -13238,7 +13530,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
       <c r="O233" t="inlineStr">
         <is>
           <t>New</t>
@@ -13306,7 +13602,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
     </row>
@@ -13362,7 +13662,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
     </row>
@@ -13422,7 +13726,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
       <c r="O236" t="inlineStr">
         <is>
           <t>New</t>
@@ -13486,7 +13794,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
       <c r="O237" t="inlineStr">
         <is>
           <t>New</t>
@@ -13558,7 +13870,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="O238" t="inlineStr">
         <is>
           <t>New</t>
@@ -13622,7 +13938,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
       <c r="O239" t="inlineStr">
         <is>
           <t>New</t>
@@ -13686,7 +14006,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
       <c r="O240" t="inlineStr">
         <is>
           <t>New</t>
@@ -13750,7 +14074,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
       <c r="O241" t="inlineStr">
         <is>
           <t>New</t>
@@ -13810,7 +14138,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
       <c r="O242" t="inlineStr">
         <is>
           <t>New</t>
@@ -13870,7 +14202,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>New</t>
@@ -13938,7 +14274,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
       <c r="O244" t="inlineStr">
         <is>
           <t>New</t>
@@ -14002,7 +14342,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
       <c r="O245" t="inlineStr">
         <is>
           <t>New</t>
@@ -14070,7 +14414,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
       <c r="O246" t="inlineStr">
         <is>
           <t>New</t>
@@ -14134,7 +14482,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O247" t="inlineStr">
         <is>
           <t>New</t>
@@ -14198,7 +14550,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
       <c r="O248" t="inlineStr">
         <is>
           <t>New</t>
